--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
@@ -14761,7 +14761,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:41</t>
+    <t xml:space="preserve">2026-09-07 12:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2022.xlsx
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:58</t>
+    <t xml:space="preserve">2026-09-08 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
